--- a/data/Pajjota.xlsx
+++ b/data/Pajjota.xlsx
@@ -5,12 +5,13 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="default" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="replacement" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="inside" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="params" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="default" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="replacement" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="inside" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -22,15 +23,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
+  <si>
+    <t xml:space="preserve">name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">timezon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Europe/Brussels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">routing</t>
+  </si>
   <si>
     <t xml:space="preserve">table</t>
   </si>
   <si>
     <t xml:space="preserve">field</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value</t>
   </si>
   <si>
     <t xml:space="preserve">type</t>
@@ -297,11 +313,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="27.96"/>
-  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -310,39 +323,29 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>9</v>
+      <c r="B3" s="1" t="n">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>7011</v>
       </c>
     </row>
   </sheetData>
@@ -357,6 +360,70 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="27.96"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -371,46 +438,46 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -424,7 +491,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -434,13 +501,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/data/Pajjota.xlsx
+++ b/data/Pajjota.xlsx
@@ -9,9 +9,8 @@
   </bookViews>
   <sheets>
     <sheet name="params" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="default" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="replacement" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="inside" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="replacement" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="inside" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -23,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
   <si>
     <t xml:space="preserve">name</t>
   </si>
@@ -40,34 +39,13 @@
     <t xml:space="preserve">location</t>
   </si>
   <si>
-    <t xml:space="preserve">routing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">table</t>
-  </si>
-  <si>
-    <t xml:space="preserve">field</t>
-  </si>
-  <si>
-    <t xml:space="preserve">type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">timetables</t>
-  </si>
-  <si>
     <t xml:space="preserve">gong_id</t>
   </si>
   <si>
-    <t xml:space="preserve">int</t>
-  </si>
-  <si>
     <t xml:space="preserve">targets</t>
   </si>
   <si>
     <t xml:space="preserve">CC MA MA-D FA KDB DH1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">str</t>
   </si>
   <si>
     <t xml:space="preserve">period_type</t>
@@ -313,8 +291,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="23.37"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -345,7 +326,15 @@
         <v>5</v>
       </c>
       <c r="B4" s="1" t="n">
-        <v>7011</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -360,70 +349,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="27.96"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -438,46 +363,46 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -491,7 +416,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -501,13 +426,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/data/Pajjota.xlsx
+++ b/data/Pajjota.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
   <si>
     <t xml:space="preserve">name</t>
   </si>
@@ -48,6 +48,12 @@
     <t xml:space="preserve">CC MA MA-D FA KDB DH1</t>
   </si>
   <si>
+    <t xml:space="preserve">default_period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IN BETWEEN</t>
+  </si>
+  <si>
     <t xml:space="preserve">period_type</t>
   </si>
   <si>
@@ -64,9 +70,6 @@
   </si>
   <si>
     <t xml:space="preserve">TRUSTMEETING</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IN BETWEEN</t>
   </si>
   <si>
     <t xml:space="preserve">ServicePeriod</t>
@@ -94,7 +97,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -115,6 +118,11 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -159,12 +167,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -291,50 +307,59 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="23.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.37"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>1370</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -356,53 +381,53 @@
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="14.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="15.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="17.95"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="C3" s="2" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>18</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -425,14 +450,14 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>20</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/data/Pajjota.xlsx
+++ b/data/Pajjota.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="params" sheetId="1" state="visible" r:id="rId3"/>
@@ -97,7 +97,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -118,11 +118,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -167,7 +162,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -177,10 +172,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -204,37 +195,37 @@
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -310,7 +301,7 @@
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.37"/>
   </cols>
   <sheetData>
@@ -355,10 +346,10 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -446,8 +437,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.75"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
@@ -459,6 +453,11 @@
       <c r="C1" s="2" t="s">
         <v>21</v>
       </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/data/Pajjota.xlsx
+++ b/data/Pajjota.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="params" sheetId="1" state="visible" r:id="rId3"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
   <si>
     <t xml:space="preserve">name</t>
   </si>
@@ -82,6 +82,15 @@
   </si>
   <si>
     <t xml:space="preserve">SITSERVE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Children / teens (3d)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Child-Teen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COURSEFORBOYS</t>
   </si>
   <si>
     <t xml:space="preserve">action</t>
@@ -369,10 +378,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="14.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="17.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="15.2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="17.95"/>
   </cols>
@@ -419,6 +428,17 @@
       </c>
       <c r="C4" s="2" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -445,13 +465,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/data/Pajjota.xlsx
+++ b/data/Pajjota.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="params" sheetId="1" state="visible" r:id="rId3"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
   <si>
     <t xml:space="preserve">name</t>
   </si>
@@ -97,6 +97,9 @@
   </si>
   <si>
     <t xml:space="preserve">container</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fillin</t>
   </si>
 </sst>
 </file>
@@ -475,8 +478,12 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
+      <c r="A2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="C2" s="2"/>
     </row>
   </sheetData>

--- a/data/Pajjota.xlsx
+++ b/data/Pajjota.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="params" sheetId="1" state="visible" r:id="rId3"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
   <si>
     <t xml:space="preserve">name</t>
   </si>
@@ -97,9 +97,6 @@
   </si>
   <si>
     <t xml:space="preserve">container</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fillin</t>
   </si>
 </sst>
 </file>
@@ -478,12 +475,8 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
       <c r="C2" s="2"/>
     </row>
   </sheetData>
